--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487210_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487210_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0953</v>
+        <v>4.3888</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1877</v>
+        <v>1.5883</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9076</v>
+        <v>2.8005</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0583</v>
@@ -610,13 +610,13 @@
         <v>3.0881</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8778</v>
+        <v>-0.4772</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1242</v>
+        <v>0.0172</v>
       </c>
       <c r="V2" t="n">
         <v>2.784</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6688</v>
+        <v>0.9876</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6954</v>
+        <v>-1.2962</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3641</v>
+        <v>2.2838</v>
       </c>
       <c r="G3" t="n">
         <v>0.4162</v>
@@ -688,13 +688,13 @@
         <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4805</v>
+        <v>-0.2006</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6808</v>
+        <v>0.08</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2003</v>
+        <v>-0.2806</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>A. YAILO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5633</v>
+        <v>0.6979</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2383</v>
+        <v>-0.6116</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8015</v>
+        <v>1.3095</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.6217</v>
+        <v>1.6921</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2151</v>
+        <v>2.5189</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4066</v>
+        <v>-0.8268</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8077</v>
+        <v>1.5779</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5538999999999999</v>
+        <v>2.2455</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2538</v>
+        <v>-0.6676</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8141</v>
+        <v>0.1142</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6612</v>
+        <v>0.2734</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1528</v>
+        <v>-0.1592</v>
       </c>
       <c r="P4" t="n">
         <v>1.7371</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7021</v>
+        <v>3.8602</v>
       </c>
       <c r="S4" t="n">
-        <v>1.162</v>
+        <v>-0.5612</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0206</v>
+        <v>-0.6381</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1414</v>
+        <v>0.077</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2859</v>
+        <v>-2.1701</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5138</v>
+        <v>0.5717</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. YAILO</t>
+          <t>A. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1904</v>
+        <v>-0.1007</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3125</v>
+        <v>-0.6657</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1221</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6921</v>
+        <v>-0.4533</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5189</v>
+        <v>0.2143</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8268</v>
+        <v>-0.6676</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5779</v>
+        <v>-0.6469</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2455</v>
+        <v>0.0207</v>
       </c>
       <c r="L5" t="n">
         <v>-0.6676</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1142</v>
+        <v>0.1936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2734</v>
+        <v>0.1936</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1592</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1231</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.8602</v>
+        <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4495</v>
+        <v>-0.0334</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3391</v>
+        <v>-0.0188</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1104</v>
+        <v>-0.0145</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1701</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GOMEZ FERNANDEZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2008</v>
+        <v>-0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7659</v>
+        <v>-0.5765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3665</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4533</v>
+        <v>3.2343</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2143</v>
+        <v>1.7512</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6676</v>
+        <v>1.483</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6469</v>
+        <v>3.5678</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>2.339</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6676</v>
+        <v>1.2288</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1936</v>
+        <v>-0.3336</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1936</v>
+        <v>-0.5878</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.2542</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1335</v>
+        <v>-0.4792</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.119</v>
+        <v>-0.3771</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0145</v>
+        <v>-0.1021</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2768</v>
+        <v>-0.4847</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-1.3398</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1831</v>
+        <v>0.8551</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4978</v>
+        <v>-2.6217</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9915</v>
+        <v>-1.2151</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5062</v>
+        <v>-1.4066</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5234</v>
+        <v>-1.8077</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5641</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>-1.2538</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.8141</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4274</v>
+        <v>-0.6612</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.1528</v>
       </c>
       <c r="P7" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4297</v>
+        <v>-0.0809</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2472</v>
+        <v>0.195</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7375</v>
+        <v>-0.7309</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0772</v>
+        <v>-0.4943</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3398</v>
+        <v>-0.2366</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2343</v>
+        <v>-1.4978</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7512</v>
+        <v>-0.9915</v>
       </c>
       <c r="I8" t="n">
-        <v>1.483</v>
+        <v>-0.5062</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5678</v>
+        <v>-0.5234</v>
       </c>
       <c r="K8" t="n">
-        <v>2.339</v>
+        <v>-0.5641</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2288</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3336</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5878</v>
+        <v>-0.4274</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2542</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0067</v>
+        <v>0.2228</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8778</v>
+        <v>0.0291</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1289</v>
+        <v>0.1937</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5138</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8116</v>
+        <v>-1.0654</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3516</v>
+        <v>-3.5519</v>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>2.4865</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0883</v>
@@ -1156,13 +1156,13 @@
         <v>2.3161</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0211</v>
+        <v>-0.275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0912</v>
+        <v>-0.2915</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="V9" t="n">
         <v>1.842</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5443</v>
+        <v>-1.4441</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.4114</v>
       </c>
       <c r="F10" t="n">
         <v>-1.0327</v>
@@ -1234,10 +1234,10 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5208</v>
+        <v>-0.4207</v>
       </c>
       <c r="U10" t="n">
         <v>0.1639</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0989</v>
+        <v>-2.4667</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.614</v>
+        <v>-2.7141</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5151</v>
+        <v>0.2474</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4109</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.074</v>
+        <v>-0.4419</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0132</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0873</v>
+        <v>-0.355</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9603</v>
+        <v>-4.065</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9136</v>
+        <v>-4.3127</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0467</v>
+        <v>0.2477</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1798</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8686</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1607</v>
+        <v>-0.5598</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7079</v>
+        <v>-0.4135</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
@@ -1426,7 +1426,7 @@
         <v>-4.4932</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.3862</v>
+        <v>-14.3859</v>
       </c>
       <c r="F13" t="n">
         <v>9.8927</v>
@@ -1453,7 +1453,7 @@
         <v>-0.8986000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.77</v>
+        <v>-0.7700000000000002</v>
       </c>
       <c r="O13" t="n">
         <v>-0.1284</v>
@@ -1468,13 +1468,13 @@
         <v>23.16090000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.3444</v>
+        <v>-3.3446</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.8421</v>
+        <v>-2.8419</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5025999999999999</v>
+        <v>-0.5024</v>
       </c>
       <c r="V13" t="n">
         <v>-4.298</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7553</v>
+        <v>5.0374</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3186</v>
+        <v>1.217</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4367</v>
+        <v>3.8204</v>
       </c>
       <c r="G14" t="n">
         <v>0.2623</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7788</v>
+        <v>2.0609</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8667</v>
+        <v>0.7651</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9122</v>
+        <v>1.2958</v>
       </c>
       <c r="V14" t="n">
         <v>1.5561</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0889</v>
+        <v>2.4634</v>
       </c>
       <c r="E15" t="n">
         <v>0.1118</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9771</v>
+        <v>2.3515</v>
       </c>
       <c r="G15" t="n">
         <v>1.969</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4131</v>
+        <v>0.7876</v>
       </c>
       <c r="T15" t="n">
         <v>0.0278</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3853</v>
+        <v>0.7598</v>
       </c>
       <c r="V15" t="n">
         <v>0.2859</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9837</v>
+        <v>1.6503</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1295</v>
+        <v>-1.3284</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1132</v>
+        <v>2.9787</v>
       </c>
       <c r="G16" t="n">
         <v>0.5528</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1209</v>
+        <v>0.7876</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6253</v>
+        <v>0.1759</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7462</v>
+        <v>0.6117</v>
       </c>
       <c r="V16" t="n">
         <v>3.398</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9675</v>
+        <v>0.2533</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.35</v>
+        <v>-2.2513</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3175</v>
+        <v>2.5046</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8416</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2374</v>
+        <v>0.5232</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3775</v>
+        <v>0.4763</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1402</v>
+        <v>0.0469</v>
       </c>
       <c r="V17" t="n">
         <v>0.5717</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0205</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2319</v>
+        <v>-0.9398</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2115</v>
+        <v>1.0055</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1583</v>
+        <v>-1.1401</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7306</v>
+        <v>-1.7492</v>
       </c>
       <c r="I18" t="n">
-        <v>0.889</v>
+        <v>0.6091</v>
       </c>
       <c r="J18" t="n">
-        <v>0.759</v>
+        <v>-0.8865</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1242</v>
+        <v>-0.9679</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6348</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6006</v>
+        <v>-0.2537</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8548</v>
+        <v>-0.7813</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2542</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.579</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6861</v>
+        <v>-0.3153</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1322</v>
+        <v>-0.3163</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2859</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2859</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2754</v>
+        <v>-0.2387</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0399</v>
+        <v>-1.0252</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7865</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1401</v>
+        <v>2.6497</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7492</v>
+        <v>1.8536</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6091</v>
+        <v>0.7961</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8865</v>
+        <v>2.5227</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9679</v>
+        <v>2.5148</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0814</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2537</v>
+        <v>0.127</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7813</v>
+        <v>-0.6612</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.7883</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6564</v>
+        <v>0.1418</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4164</v>
+        <v>-0.3946</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2399</v>
+        <v>0.5364</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9421</v>
+        <v>-0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>1.228</v>
+        <v>0.8999</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.2716</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2255</v>
+        <v>-1.9094</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6262</v>
+        <v>1.6378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6497</v>
+        <v>1.1747</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8536</v>
+        <v>1.0133</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7961</v>
+        <v>0.1614</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5227</v>
+        <v>0.7806</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5148</v>
+        <v>1.4075</v>
       </c>
       <c r="L20" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="M20" t="n">
-        <v>0.127</v>
+        <v>0.3941</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6612</v>
+        <v>-0.3942</v>
       </c>
       <c r="O20" t="n">
         <v>0.7883</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7021</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q20" t="n">
         <v>-4.0532</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2188</v>
+        <v>0.4488</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5949</v>
+        <v>0.1352</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3761</v>
+        <v>0.3136</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3281</v>
+        <v>0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8999</v>
+        <v>1.228</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.468</v>
+        <v>-0.428</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1616</v>
+        <v>-1.5323</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3064</v>
+        <v>1.1044</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4752</v>
+        <v>0.1583</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0746</v>
+        <v>-0.7306</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4006</v>
+        <v>0.889</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0414</v>
+        <v>0.759</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0414</v>
+        <v>0.1242</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6348</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4338</v>
+        <v>-0.6006</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0332</v>
+        <v>-0.8548</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4006</v>
+        <v>0.2542</v>
       </c>
       <c r="P21" t="n">
         <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R21" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1362</v>
+        <v>0.2786</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.238</v>
+        <v>-0.1682</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1018</v>
+        <v>0.4468</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6147</v>
+        <v>-1.1273</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6104</v>
+        <v>-1.0615</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9956</v>
+        <v>-0.0658</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1747</v>
+        <v>0.4752</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0133</v>
+        <v>0.0746</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1614</v>
+        <v>0.4006</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7806</v>
+        <v>0.0414</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4075</v>
+        <v>0.0414</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6269</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3941</v>
+        <v>0.4338</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3942</v>
+        <v>0.0332</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7883</v>
+        <v>0.4006</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5091</v>
+        <v>-0.579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8943</v>
+        <v>0.2046</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5658</v>
+        <v>-0.1378</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3285</v>
+        <v>0.3424</v>
       </c>
       <c r="V22" t="n">
-        <v>0.614</v>
+        <v>-1.228</v>
       </c>
       <c r="W22" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3242</v>
+        <v>-1.576</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5743</v>
+        <v>-1.1738</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7499</v>
+        <v>-0.4022</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6891</v>
@@ -2248,13 +2248,13 @@
         <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9862</v>
+        <v>-0.238</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4614</v>
+        <v>-0.0608</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5248</v>
+        <v>-0.1772</v>
       </c>
       <c r="V23" t="n">
         <v>-1.228</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.493300000000001</v>
+        <v>5.8285</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.892700000000001</v>
+        <v>-9.892899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3861</v>
+        <v>15.7214</v>
       </c>
       <c r="G24" t="n">
-        <v>4.571200000000001</v>
+        <v>4.5712</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.1399</v>
+        <v>-4.139900000000001</v>
       </c>
       <c r="I24" t="n">
         <v>8.711200000000002</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8986000000000002</v>
+        <v>0.8986000000000006</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7698</v>
+        <v>0.7698000000000005</v>
       </c>
       <c r="L24" t="n">
         <v>0.1287000000000001</v>
@@ -2311,10 +2311,10 @@
         <v>3.672700000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.909800000000001</v>
+        <v>-4.9098</v>
       </c>
       <c r="O24" t="n">
-        <v>8.582599999999999</v>
+        <v>8.582600000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-7.720300000000001</v>
@@ -2326,13 +2326,13 @@
         <v>15.4409</v>
       </c>
       <c r="S24" t="n">
-        <v>3.344399999999999</v>
+        <v>4.6798</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5024000000000002</v>
+        <v>0.5025999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.8421</v>
+        <v>4.1772</v>
       </c>
       <c r="V24" t="n">
         <v>4.297800000000001</v>
@@ -2341,7 +2341,7 @@
         <v>11.8671</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.569399999999999</v>
+        <v>-7.5694</v>
       </c>
     </row>
   </sheetData>
